--- a/Datos Tesis Upstream/Estructura de Datos/2526-3/Asistencia y Participaciones Estructura de Datos 2526-3.xlsx
+++ b/Datos Tesis Upstream/Estructura de Datos/2526-3/Asistencia y Participaciones Estructura de Datos 2526-3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nelsoncarrillo/Downloads/tesis-prediccion-participacion/Datos Tesis Upstream/Estructura de Datos/2526-3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CC8097-3AC4-314F-8E02-E85052AF337A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3130B3FE-D123-1248-9B55-F116CB3686EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lista" sheetId="1" r:id="rId1"/>
@@ -47,6 +47,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizarra</t>
@@ -60,6 +61,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Llegó tarde
@@ -74,6 +76,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Llegó tarde
@@ -88,6 +91,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica CRC</t>
@@ -101,6 +105,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Entrega Proy</t>
@@ -114,6 +119,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica CRC</t>
@@ -127,6 +133,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica CRC</t>
@@ -140,6 +147,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizarra</t>
@@ -153,6 +161,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizarra</t>
@@ -166,6 +175,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica CRC</t>
@@ -179,6 +189,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizarra</t>
@@ -192,6 +203,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizarra</t>
@@ -205,6 +217,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Entrega Proyecto</t>
@@ -218,6 +231,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizarra</t>
@@ -231,6 +245,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Llegó tarde
@@ -245,6 +260,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizzarra + 2 intervenciones</t>
@@ -258,6 +274,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Entrega Proy</t>
@@ -271,6 +288,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>2 pizarra</t>
@@ -284,6 +302,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizarra</t>
@@ -297,6 +316,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica CRC</t>
@@ -310,6 +330,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Entrega Proy</t>
@@ -323,6 +344,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Ausencia justificada</t>
@@ -336,6 +358,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Ausencia justificada</t>
@@ -349,6 +372,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Ausencia justificada</t>
@@ -362,6 +386,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Ausencia justificada</t>
@@ -375,6 +400,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Tarde
@@ -389,6 +415,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica CRC</t>
@@ -402,6 +429,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizzarra + 1 intervención</t>
@@ -415,6 +443,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Entrega Proyecto
@@ -429,6 +458,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Entrega Proy + intervención</t>
@@ -442,6 +472,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica CRC</t>
@@ -455,6 +486,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Entrega Proy</t>
@@ -468,6 +500,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>pero regresó</t>
@@ -481,6 +514,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>pero regresó</t>
@@ -494,6 +528,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica CRC</t>
@@ -507,6 +542,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Entrega Proy</t>
@@ -520,6 +556,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Entrega Proyecto
@@ -534,6 +571,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>1 intervención, jubilado</t>
@@ -547,6 +585,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizzarra + 2 intervenciones</t>
@@ -560,6 +599,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Entrega Proy, llegó tarde</t>
@@ -573,6 +613,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Llegó tarde
@@ -587,6 +628,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>2 pizarra, 1 intervención, jubilado</t>
@@ -600,6 +642,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Llegó 12:30</t>
@@ -613,6 +656,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Llegó 12:30</t>
@@ -626,6 +670,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizarra</t>
@@ -639,6 +684,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizarra</t>
@@ -652,6 +698,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizarra</t>
@@ -665,6 +712,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Llegó tarde
@@ -679,6 +727,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizarra</t>
@@ -692,6 +741,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Llegó 1:15</t>
@@ -705,6 +755,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica CRC</t>
@@ -718,6 +769,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica CRC</t>
@@ -731,6 +783,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Entrega Proy + intervención</t>
@@ -744,6 +797,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Entrega Proy + intervención</t>
@@ -757,6 +811,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizarra + intervención</t>
@@ -770,6 +825,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Tarde</t>
@@ -783,6 +839,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>2 pizarra, 1 intervención, tarde</t>
@@ -796,6 +853,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizarra</t>
@@ -809,6 +867,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>pero regresó</t>
@@ -822,6 +881,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Entrega Proy</t>
@@ -838,26 +898,28 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="M7" authorId="0" shapeId="0" xr:uid="{113F0709-B67D-E74F-BB3D-2922C76C18DB}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="N7" authorId="0" shapeId="0" xr:uid="{113F0709-B67D-E74F-BB3D-2922C76C18DB}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizarra</t>
         </r>
       </text>
     </comment>
-    <comment ref="U7" authorId="0" shapeId="0" xr:uid="{94B43AD7-F3B4-F348-BB82-3FD20C8CC986}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="V7" authorId="0" shapeId="0" xr:uid="{94B43AD7-F3B4-F348-BB82-3FD20C8CC986}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Llegó tarde
@@ -865,13 +927,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y7" authorId="0" shapeId="0" xr:uid="{FFFFA4EE-C5DC-0C44-90BF-1B65900B5D13}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="Z7" authorId="0" shapeId="0" xr:uid="{FFFFA4EE-C5DC-0C44-90BF-1B65900B5D13}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Llegó tarde
@@ -879,150 +942,161 @@
         </r>
       </text>
     </comment>
-    <comment ref="J8" authorId="0" shapeId="0" xr:uid="{D88D49A5-CC30-1449-A41D-665729CB0B3F}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="K8" authorId="0" shapeId="0" xr:uid="{D88D49A5-CC30-1449-A41D-665729CB0B3F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica CRC</t>
         </r>
       </text>
     </comment>
-    <comment ref="L8" authorId="0" shapeId="0" xr:uid="{40473A9D-C14F-764E-BFBE-5C0E2BBF3CBA}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="M8" authorId="0" shapeId="0" xr:uid="{40473A9D-C14F-764E-BFBE-5C0E2BBF3CBA}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Entrega Proy</t>
         </r>
       </text>
     </comment>
-    <comment ref="J10" authorId="0" shapeId="0" xr:uid="{45AE1A3D-0F21-DD4E-B299-6F8060F5990B}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="K10" authorId="0" shapeId="0" xr:uid="{45AE1A3D-0F21-DD4E-B299-6F8060F5990B}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica CRC</t>
         </r>
       </text>
     </comment>
-    <comment ref="K10" authorId="0" shapeId="0" xr:uid="{F6B6D2C8-120D-CA45-AFE3-D72F506B4917}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="L10" authorId="0" shapeId="0" xr:uid="{F6B6D2C8-120D-CA45-AFE3-D72F506B4917}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica CRC</t>
         </r>
       </text>
     </comment>
-    <comment ref="M10" authorId="0" shapeId="0" xr:uid="{640ED6DE-E676-2746-AB95-F7DEA5488A9B}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="N10" authorId="0" shapeId="0" xr:uid="{640ED6DE-E676-2746-AB95-F7DEA5488A9B}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizarra</t>
         </r>
       </text>
     </comment>
-    <comment ref="U10" authorId="0" shapeId="0" xr:uid="{ADC9E4C8-4A9F-4E40-B6E2-DE3DC0821287}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="V10" authorId="0" shapeId="0" xr:uid="{ADC9E4C8-4A9F-4E40-B6E2-DE3DC0821287}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizarra</t>
         </r>
       </text>
     </comment>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{3CF50EA1-28E0-1245-B427-85E92BE6AD11}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="K11" authorId="0" shapeId="0" xr:uid="{3CF50EA1-28E0-1245-B427-85E92BE6AD11}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica CRC</t>
         </r>
       </text>
     </comment>
-    <comment ref="M11" authorId="0" shapeId="0" xr:uid="{2B5E39AE-DA31-754F-B154-5B0AD996ACD7}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="N11" authorId="0" shapeId="0" xr:uid="{2B5E39AE-DA31-754F-B154-5B0AD996ACD7}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizarra</t>
         </r>
       </text>
     </comment>
-    <comment ref="Q11" authorId="0" shapeId="0" xr:uid="{5F9254FD-65B5-ED4A-B2A9-7EA26E779564}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="R11" authorId="0" shapeId="0" xr:uid="{5F9254FD-65B5-ED4A-B2A9-7EA26E779564}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizarra</t>
         </r>
       </text>
     </comment>
-    <comment ref="T11" authorId="0" shapeId="0" xr:uid="{A6B9FB9D-58CD-9C42-B5B5-7D2266B5012E}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="U11" authorId="0" shapeId="0" xr:uid="{A6B9FB9D-58CD-9C42-B5B5-7D2266B5012E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Entrega Proyecto</t>
         </r>
       </text>
     </comment>
-    <comment ref="U11" authorId="0" shapeId="0" xr:uid="{CF76F390-7932-764C-B380-0D9B55A43BEC}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="V11" authorId="0" shapeId="0" xr:uid="{CF76F390-7932-764C-B380-0D9B55A43BEC}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizarra</t>
         </r>
       </text>
     </comment>
-    <comment ref="X11" authorId="0" shapeId="0" xr:uid="{8AB9D707-326A-BF40-9A03-BC6FD93ED19F}">
+    <comment ref="Y11" authorId="0" shapeId="0" xr:uid="{8AB9D707-326A-BF40-9A03-BC6FD93ED19F}">
       <text>
         <r>
           <rPr>
@@ -1045,143 +1119,154 @@
         </r>
       </text>
     </comment>
-    <comment ref="K13" authorId="0" shapeId="0" xr:uid="{823FE621-9A02-E441-A6A9-8A44B14DA986}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="L13" authorId="0" shapeId="0" xr:uid="{823FE621-9A02-E441-A6A9-8A44B14DA986}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizzarra + 2 intervenciones</t>
         </r>
       </text>
     </comment>
-    <comment ref="N13" authorId="0" shapeId="0" xr:uid="{8A659516-2F25-C041-A15F-CDC74B8C2187}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="O13" authorId="0" shapeId="0" xr:uid="{8A659516-2F25-C041-A15F-CDC74B8C2187}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Entrega Proy</t>
         </r>
       </text>
     </comment>
-    <comment ref="Y13" authorId="0" shapeId="0" xr:uid="{AA3F094A-F799-0C40-8366-19FDB7906316}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="Z13" authorId="0" shapeId="0" xr:uid="{AA3F094A-F799-0C40-8366-19FDB7906316}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>2 pizarra</t>
         </r>
       </text>
     </comment>
-    <comment ref="X16" authorId="0" shapeId="0" xr:uid="{7CB47D55-C032-654D-9C95-13438624C059}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="Y16" authorId="0" shapeId="0" xr:uid="{7CB47D55-C032-654D-9C95-13438624C059}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizarra</t>
         </r>
       </text>
     </comment>
-    <comment ref="J17" authorId="0" shapeId="0" xr:uid="{1219ACA0-EB1F-E34A-B130-128F3E8DD613}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="K17" authorId="0" shapeId="0" xr:uid="{1219ACA0-EB1F-E34A-B130-128F3E8DD613}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica CRC</t>
         </r>
       </text>
     </comment>
-    <comment ref="L17" authorId="0" shapeId="0" xr:uid="{CA4E6166-8712-6C44-ACD4-4D1EE5A0CD49}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="M17" authorId="0" shapeId="0" xr:uid="{CA4E6166-8712-6C44-ACD4-4D1EE5A0CD49}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Entrega Proy</t>
         </r>
       </text>
     </comment>
-    <comment ref="M17" authorId="0" shapeId="0" xr:uid="{0FD07A98-B161-B549-AEBB-EB1FD14D7D5D}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="N17" authorId="0" shapeId="0" xr:uid="{0FD07A98-B161-B549-AEBB-EB1FD14D7D5D}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Ausencia justificada</t>
         </r>
       </text>
     </comment>
-    <comment ref="N17" authorId="0" shapeId="0" xr:uid="{4685395B-0C69-024F-A09A-008DEDE70DC1}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="O17" authorId="0" shapeId="0" xr:uid="{4685395B-0C69-024F-A09A-008DEDE70DC1}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Ausencia justificada</t>
         </r>
       </text>
     </comment>
-    <comment ref="P17" authorId="0" shapeId="0" xr:uid="{4A9C5C18-3DB8-9041-A236-4ACFF11E0DCE}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="Q17" authorId="0" shapeId="0" xr:uid="{4A9C5C18-3DB8-9041-A236-4ACFF11E0DCE}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Ausencia justificada</t>
         </r>
       </text>
     </comment>
-    <comment ref="Q17" authorId="0" shapeId="0" xr:uid="{EEE8746D-DE76-2E4B-89CB-372E331A9986}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="R17" authorId="0" shapeId="0" xr:uid="{EEE8746D-DE76-2E4B-89CB-372E331A9986}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Ausencia justificada</t>
         </r>
       </text>
     </comment>
-    <comment ref="V17" authorId="0" shapeId="0" xr:uid="{0499196B-AA7C-EB46-8579-B547E97D084E}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="W17" authorId="0" shapeId="0" xr:uid="{0499196B-AA7C-EB46-8579-B547E97D084E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Tarde
@@ -1189,39 +1274,42 @@
         </r>
       </text>
     </comment>
-    <comment ref="J18" authorId="0" shapeId="0" xr:uid="{5C772944-4C50-7D41-B378-F4A4EE80146E}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="K18" authorId="0" shapeId="0" xr:uid="{5C772944-4C50-7D41-B378-F4A4EE80146E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica CRC</t>
         </r>
       </text>
     </comment>
-    <comment ref="K19" authorId="0" shapeId="0" xr:uid="{97D11828-8835-924E-98A3-796FEE83D20C}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="L19" authorId="0" shapeId="0" xr:uid="{97D11828-8835-924E-98A3-796FEE83D20C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizzarra + 1 intervención</t>
         </r>
       </text>
     </comment>
-    <comment ref="T20" authorId="0" shapeId="0" xr:uid="{0CFC2C83-6ACE-5444-AC4B-066757C77A3A}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="U20" authorId="0" shapeId="0" xr:uid="{0CFC2C83-6ACE-5444-AC4B-066757C77A3A}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Entrega Proyecto
@@ -1229,104 +1317,112 @@
         </r>
       </text>
     </comment>
-    <comment ref="L22" authorId="0" shapeId="0" xr:uid="{AF08E069-4BB1-0040-B7E4-9EB3541019F4}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="M22" authorId="0" shapeId="0" xr:uid="{AF08E069-4BB1-0040-B7E4-9EB3541019F4}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Entrega Proy + intervención</t>
         </r>
       </text>
     </comment>
-    <comment ref="J23" authorId="0" shapeId="0" xr:uid="{761815B6-CE2F-FD40-AF9E-82E256A3FF4E}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="K23" authorId="0" shapeId="0" xr:uid="{761815B6-CE2F-FD40-AF9E-82E256A3FF4E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica CRC</t>
         </r>
       </text>
     </comment>
-    <comment ref="L24" authorId="0" shapeId="0" xr:uid="{70907F76-AC53-304F-AEA4-5F0370BABA3C}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="M24" authorId="0" shapeId="0" xr:uid="{70907F76-AC53-304F-AEA4-5F0370BABA3C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Entrega Proy</t>
         </r>
       </text>
     </comment>
-    <comment ref="H26" authorId="0" shapeId="0" xr:uid="{D2EAD9F7-C39A-CD4B-8E64-E9D837AE26F9}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="I26" authorId="0" shapeId="0" xr:uid="{D2EAD9F7-C39A-CD4B-8E64-E9D837AE26F9}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>pero regresó</t>
         </r>
       </text>
     </comment>
-    <comment ref="I26" authorId="0" shapeId="0" xr:uid="{1A795749-21B8-4C4A-B272-2F363ABC67FA}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="J26" authorId="0" shapeId="0" xr:uid="{1A795749-21B8-4C4A-B272-2F363ABC67FA}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>pero regresó</t>
         </r>
       </text>
     </comment>
-    <comment ref="J26" authorId="0" shapeId="0" xr:uid="{EB98D055-748E-4349-A7F0-45F017424085}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="K26" authorId="0" shapeId="0" xr:uid="{EB98D055-748E-4349-A7F0-45F017424085}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica CRC</t>
         </r>
       </text>
     </comment>
-    <comment ref="L26" authorId="0" shapeId="0" xr:uid="{5032D0A2-1A90-1C49-A81B-5ECCD2E7AA73}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="M26" authorId="0" shapeId="0" xr:uid="{5032D0A2-1A90-1C49-A81B-5ECCD2E7AA73}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Entrega Proy</t>
         </r>
       </text>
     </comment>
-    <comment ref="T26" authorId="0" shapeId="0" xr:uid="{BD71D2BF-C16A-C840-B2F3-EDDC56832ECE}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="U26" authorId="0" shapeId="0" xr:uid="{BD71D2BF-C16A-C840-B2F3-EDDC56832ECE}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Entrega Proyecto
@@ -1334,52 +1430,56 @@
         </r>
       </text>
     </comment>
-    <comment ref="W26" authorId="0" shapeId="0" xr:uid="{594E89A6-EC8B-B745-960A-81B8AF531787}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="X26" authorId="0" shapeId="0" xr:uid="{594E89A6-EC8B-B745-960A-81B8AF531787}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>1 intervención, jubilado</t>
         </r>
       </text>
     </comment>
-    <comment ref="G28" authorId="0" shapeId="0" xr:uid="{5DEADD3B-75ED-5544-BC7D-58E18F3D25A8}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="H28" authorId="0" shapeId="0" xr:uid="{5DEADD3B-75ED-5544-BC7D-58E18F3D25A8}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizzarra + 2 intervenciones</t>
         </r>
       </text>
     </comment>
-    <comment ref="N28" authorId="0" shapeId="0" xr:uid="{2867437F-91DC-B841-B1C6-A037B1103C31}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="O28" authorId="0" shapeId="0" xr:uid="{2867437F-91DC-B841-B1C6-A037B1103C31}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Entrega Proy, llegó tarde</t>
         </r>
       </text>
     </comment>
-    <comment ref="Q28" authorId="0" shapeId="0" xr:uid="{A50D6E29-D279-E147-90EF-0066A398AD3D}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="R28" authorId="0" shapeId="0" xr:uid="{A50D6E29-D279-E147-90EF-0066A398AD3D}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Llegó tarde
@@ -1387,91 +1487,98 @@
         </r>
       </text>
     </comment>
-    <comment ref="W28" authorId="0" shapeId="0" xr:uid="{9C0B7C10-7076-544C-A9AB-D59C38431BEE}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="X28" authorId="0" shapeId="0" xr:uid="{9C0B7C10-7076-544C-A9AB-D59C38431BEE}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>2 pizarra, 1 intervención, jubilado</t>
         </r>
       </text>
     </comment>
-    <comment ref="E29" authorId="0" shapeId="0" xr:uid="{61871279-5A7E-C04D-9939-DEEA07FEA14D}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="F29" authorId="0" shapeId="0" xr:uid="{61871279-5A7E-C04D-9939-DEEA07FEA14D}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Llegó 12:30</t>
         </r>
       </text>
     </comment>
-    <comment ref="G30" authorId="0" shapeId="0" xr:uid="{C24DF262-8B74-ED43-8C99-2866A1EC347C}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="H30" authorId="0" shapeId="0" xr:uid="{C24DF262-8B74-ED43-8C99-2866A1EC347C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Llegó 12:30</t>
         </r>
       </text>
     </comment>
-    <comment ref="M31" authorId="0" shapeId="0" xr:uid="{9005E626-EBAB-814E-A760-608D8382B2A0}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="N31" authorId="0" shapeId="0" xr:uid="{9005E626-EBAB-814E-A760-608D8382B2A0}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizarra</t>
         </r>
       </text>
     </comment>
-    <comment ref="T31" authorId="0" shapeId="0" xr:uid="{F966A910-6AE8-374F-9273-4E3831F67ACF}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="U31" authorId="0" shapeId="0" xr:uid="{F966A910-6AE8-374F-9273-4E3831F67ACF}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizarra</t>
         </r>
       </text>
     </comment>
-    <comment ref="X31" authorId="0" shapeId="0" xr:uid="{A996BD80-6C98-7C40-AD88-8C04EF1CF227}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="Y31" authorId="0" shapeId="0" xr:uid="{A996BD80-6C98-7C40-AD88-8C04EF1CF227}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizarra</t>
         </r>
       </text>
     </comment>
-    <comment ref="Y31" authorId="0" shapeId="0" xr:uid="{63BF449F-22E0-5F43-8E66-A4806813A052}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="Z31" authorId="0" shapeId="0" xr:uid="{63BF449F-22E0-5F43-8E66-A4806813A052}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Llegó tarde
@@ -1479,156 +1586,168 @@
         </r>
       </text>
     </comment>
-    <comment ref="G32" authorId="0" shapeId="0" xr:uid="{21611A31-115D-D446-BCB6-6B2DCC4E0D2A}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="H32" authorId="0" shapeId="0" xr:uid="{21611A31-115D-D446-BCB6-6B2DCC4E0D2A}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizarra</t>
         </r>
       </text>
     </comment>
-    <comment ref="F33" authorId="0" shapeId="0" xr:uid="{60007D21-F488-374C-9370-5E318137DE8A}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="G33" authorId="0" shapeId="0" xr:uid="{60007D21-F488-374C-9370-5E318137DE8A}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Llegó 1:15</t>
         </r>
       </text>
     </comment>
-    <comment ref="J33" authorId="0" shapeId="0" xr:uid="{803F8DFA-B06B-F845-AE99-908821622236}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="K33" authorId="0" shapeId="0" xr:uid="{803F8DFA-B06B-F845-AE99-908821622236}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica CRC</t>
         </r>
       </text>
     </comment>
-    <comment ref="K33" authorId="0" shapeId="0" xr:uid="{38E622EC-2E76-C04C-ABEB-030B2DA9907C}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="L33" authorId="0" shapeId="0" xr:uid="{38E622EC-2E76-C04C-ABEB-030B2DA9907C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica CRC</t>
         </r>
       </text>
     </comment>
-    <comment ref="L33" authorId="0" shapeId="0" xr:uid="{2C011633-68D3-A847-A158-1380D56F8A79}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="M33" authorId="0" shapeId="0" xr:uid="{2C011633-68D3-A847-A158-1380D56F8A79}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Entrega Proy + intervención</t>
         </r>
       </text>
     </comment>
-    <comment ref="N33" authorId="0" shapeId="0" xr:uid="{C06D9AD7-1217-294A-BD3A-086571D31A21}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="O33" authorId="0" shapeId="0" xr:uid="{C06D9AD7-1217-294A-BD3A-086571D31A21}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Entrega Proy + intervención</t>
         </r>
       </text>
     </comment>
-    <comment ref="T33" authorId="0" shapeId="0" xr:uid="{C6B5DFD6-97F6-3F42-8747-50F747BE788F}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="U33" authorId="0" shapeId="0" xr:uid="{C6B5DFD6-97F6-3F42-8747-50F747BE788F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizarra + intervención</t>
         </r>
       </text>
     </comment>
-    <comment ref="V33" authorId="0" shapeId="0" xr:uid="{746E4F43-2768-7A4F-8677-42EF4B3E7753}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="W33" authorId="0" shapeId="0" xr:uid="{746E4F43-2768-7A4F-8677-42EF4B3E7753}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Tarde</t>
         </r>
       </text>
     </comment>
-    <comment ref="W33" authorId="0" shapeId="0" xr:uid="{0BA9563D-734F-024B-AB06-BD7CEDC16DBF}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="X33" authorId="0" shapeId="0" xr:uid="{0BA9563D-734F-024B-AB06-BD7CEDC16DBF}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>2 pizarra, 1 intervención, tarde</t>
         </r>
       </text>
     </comment>
-    <comment ref="Y33" authorId="0" shapeId="0" xr:uid="{865BB805-3D1D-514D-B014-610AE7DE6FBC}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="Z33" authorId="0" shapeId="0" xr:uid="{865BB805-3D1D-514D-B014-610AE7DE6FBC}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Pizarra</t>
         </r>
       </text>
     </comment>
-    <comment ref="I34" authorId="0" shapeId="0" xr:uid="{54D98CC3-24B4-F243-B225-CFC24A17239D}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="J34" authorId="0" shapeId="0" xr:uid="{54D98CC3-24B4-F243-B225-CFC24A17239D}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>pero regresó</t>
         </r>
       </text>
     </comment>
-    <comment ref="L35" authorId="0" shapeId="0" xr:uid="{A9DABB14-626A-5E44-9C6B-34B611D23A18}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
+    <comment ref="M35" authorId="0" shapeId="0" xr:uid="{A9DABB14-626A-5E44-9C6B-34B611D23A18}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Entrega Proy</t>
@@ -1640,7 +1759,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="327">
   <si>
     <t>Profesor(a):</t>
   </si>
@@ -2765,6 +2884,15 @@
   <si>
     <t>miercoles</t>
   </si>
+  <si>
+    <t>Estructura de Datos</t>
+  </si>
+  <si>
+    <t>2526-3</t>
+  </si>
+  <si>
+    <t>carnet</t>
+  </si>
 </sst>
 </file>
 
@@ -2773,7 +2901,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d\ mmm"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2850,6 +2978,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -2910,7 +3046,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2946,13 +3082,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2977,6 +3106,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -5299,58 +5438,58 @@
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="F1" s="18"/>
-      <c r="G1" s="17" t="s">
+      <c r="F1" s="29"/>
+      <c r="G1" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="19" t="s">
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="32" t="s">
         <v>233</v>
       </c>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="17" t="s">
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="19" t="s">
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="32" t="s">
         <v>245</v>
       </c>
-      <c r="Q1" s="18"/>
+      <c r="Q1" s="29"/>
       <c r="R1" s="6" t="s">
         <v>250</v>
       </c>
       <c r="S1" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="T1" s="17" t="s">
+      <c r="T1" s="31" t="s">
         <v>257</v>
       </c>
-      <c r="U1" s="18"/>
-      <c r="V1" s="19" t="s">
+      <c r="U1" s="29"/>
+      <c r="V1" s="32" t="s">
         <v>262</v>
       </c>
-      <c r="W1" s="18"/>
-      <c r="X1" s="17" t="s">
+      <c r="W1" s="29"/>
+      <c r="X1" s="31" t="s">
         <v>266</v>
       </c>
-      <c r="Y1" s="18"/>
+      <c r="Y1" s="29"/>
       <c r="Z1" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="AA1" s="17" t="s">
+      <c r="AA1" s="31" t="s">
         <v>274</v>
       </c>
-      <c r="AB1" s="18"/>
-      <c r="AC1" s="17" t="s">
+      <c r="AB1" s="29"/>
+      <c r="AC1" s="31" t="s">
         <v>278</v>
       </c>
-      <c r="AD1" s="18"/>
+      <c r="AD1" s="29"/>
     </row>
     <row r="2" spans="1:30">
       <c r="A2" s="4" t="s">
@@ -8039,572 +8178,609 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AB36"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="4" width="16" customWidth="1"/>
-    <col min="5" max="28" width="9" customWidth="1"/>
+    <col min="1" max="5" width="16" customWidth="1"/>
+    <col min="6" max="29" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="2" spans="1:28">
+      <c r="B1" s="21" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29">
       <c r="A2" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="3" spans="1:28">
+      <c r="B2" s="21" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29">
       <c r="A3" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="5" spans="1:28">
-      <c r="A5" s="18" t="s">
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29">
+      <c r="A5" s="29" t="s">
         <v>306</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="29" t="s">
         <v>307</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="29" t="s">
         <v>308</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="29" t="s">
         <v>309</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="30" t="s">
+        <v>326</v>
+      </c>
+      <c r="F5" s="29" t="s">
         <v>310</v>
       </c>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="29"/>
+      <c r="H5" s="29" t="s">
         <v>311</v>
       </c>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="29"/>
+      <c r="J5" s="29" t="s">
         <v>312</v>
       </c>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18" t="s">
+      <c r="K5" s="29"/>
+      <c r="L5" s="29" t="s">
         <v>313</v>
       </c>
-      <c r="L5" s="18"/>
-      <c r="M5" s="18" t="s">
+      <c r="M5" s="29"/>
+      <c r="N5" s="29" t="s">
         <v>314</v>
       </c>
-      <c r="N5" s="18"/>
-      <c r="O5" s="18" t="s">
+      <c r="O5" s="29"/>
+      <c r="P5" s="29" t="s">
         <v>315</v>
       </c>
-      <c r="P5" s="18"/>
-      <c r="Q5" s="18" t="s">
+      <c r="Q5" s="29"/>
+      <c r="R5" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="R5" s="18"/>
-      <c r="S5" s="18" t="s">
+      <c r="S5" s="29"/>
+      <c r="T5" s="29" t="s">
         <v>317</v>
       </c>
-      <c r="T5" s="18"/>
-      <c r="U5" s="18" t="s">
+      <c r="U5" s="29"/>
+      <c r="V5" s="29" t="s">
         <v>318</v>
       </c>
-      <c r="V5" s="18"/>
-      <c r="W5" s="18" t="s">
+      <c r="W5" s="29"/>
+      <c r="X5" s="29" t="s">
         <v>319</v>
       </c>
-      <c r="X5" s="18"/>
-      <c r="Y5" s="18" t="s">
+      <c r="Y5" s="29"/>
+      <c r="Z5" s="29" t="s">
         <v>320</v>
       </c>
-      <c r="Z5" s="18"/>
-      <c r="AA5" s="18" t="s">
+      <c r="AA5" s="29"/>
+      <c r="AB5" s="29" t="s">
         <v>321</v>
       </c>
-      <c r="AB5" s="18"/>
-    </row>
-    <row r="6" spans="1:28">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="24" t="s">
+      <c r="AC5" s="29"/>
+    </row>
+    <row r="6" spans="1:29">
+      <c r="A6" s="29"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="21" t="s">
         <v>322</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="G6" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="H6" s="21" t="s">
         <v>322</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="I6" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="I6" s="24" t="s">
+      <c r="J6" s="21" t="s">
         <v>322</v>
       </c>
-      <c r="J6" s="24" t="s">
+      <c r="K6" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="K6" s="24" t="s">
+      <c r="L6" s="21" t="s">
         <v>322</v>
       </c>
-      <c r="L6" s="24" t="s">
+      <c r="M6" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="M6" s="24" t="s">
+      <c r="N6" s="21" t="s">
         <v>322</v>
       </c>
-      <c r="N6" s="24" t="s">
+      <c r="O6" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="O6" s="24" t="s">
+      <c r="P6" s="21" t="s">
         <v>322</v>
       </c>
-      <c r="P6" s="24" t="s">
+      <c r="Q6" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="Q6" s="24" t="s">
+      <c r="R6" s="21" t="s">
         <v>322</v>
       </c>
-      <c r="R6" s="24" t="s">
+      <c r="S6" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="S6" s="24" t="s">
+      <c r="T6" s="21" t="s">
         <v>322</v>
       </c>
-      <c r="T6" s="24" t="s">
+      <c r="U6" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="U6" s="24" t="s">
+      <c r="V6" s="21" t="s">
         <v>322</v>
       </c>
-      <c r="V6" s="24" t="s">
+      <c r="W6" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="W6" s="24" t="s">
+      <c r="X6" s="21" t="s">
         <v>322</v>
       </c>
-      <c r="X6" s="24" t="s">
+      <c r="Y6" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="Y6" s="24" t="s">
+      <c r="Z6" s="21" t="s">
         <v>322</v>
       </c>
-      <c r="Z6" s="24" t="s">
+      <c r="AA6" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="AA6" s="24" t="s">
+      <c r="AB6" s="21" t="s">
         <v>322</v>
       </c>
-      <c r="AB6" s="24" t="s">
+      <c r="AC6" s="21" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="7" spans="1:28">
-      <c r="A7" s="21" t="s">
+    <row r="7" spans="1:29">
+      <c r="A7" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="H7" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="I7" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="J7" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25">
+      <c r="E7" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="I7" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="L7" s="22"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22">
         <v>2</v>
       </c>
-      <c r="N7" s="25"/>
-      <c r="P7" s="25"/>
-      <c r="Q7" s="25"/>
-      <c r="S7" s="25"/>
-      <c r="T7" s="25"/>
-      <c r="U7" s="29">
+      <c r="O7" s="22"/>
+      <c r="Q7" s="22"/>
+      <c r="R7" s="22"/>
+      <c r="T7" s="22"/>
+      <c r="U7" s="22"/>
+      <c r="V7" s="26">
         <v>2</v>
       </c>
-      <c r="V7" s="25">
+      <c r="W7" s="22">
         <v>1</v>
       </c>
-      <c r="W7" s="25"/>
-      <c r="X7" s="25" t="s">
+      <c r="X7" s="22"/>
+      <c r="Y7" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="Y7" s="29">
+      <c r="Z7" s="26">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:28">
-      <c r="A8" s="23" t="s">
+    <row r="8" spans="1:29">
+      <c r="A8" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="H8" s="26" t="s">
+      <c r="E8" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="I8" s="23" t="s">
         <v>293</v>
       </c>
-      <c r="I8" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="J8" s="26">
+      <c r="J8" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="K8" s="23">
         <v>2</v>
       </c>
-      <c r="K8" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="L8" s="26">
+      <c r="L8" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="M8" s="23">
         <v>2</v>
       </c>
-      <c r="M8" s="26">
+      <c r="N8" s="23">
         <v>1</v>
       </c>
-      <c r="N8" s="26"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="26">
+      <c r="O8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23">
         <v>1</v>
       </c>
-      <c r="S8" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="T8" s="26"/>
-      <c r="U8" s="26"/>
-      <c r="V8" s="26"/>
-      <c r="W8" s="26"/>
-      <c r="X8" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="Y8" s="26"/>
-    </row>
-    <row r="9" spans="1:28">
-      <c r="A9" s="21" t="s">
+      <c r="T8" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="U8" s="23"/>
+      <c r="V8" s="23"/>
+      <c r="W8" s="23"/>
+      <c r="X8" s="23"/>
+      <c r="Y8" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z8" s="23"/>
+    </row>
+    <row r="9" spans="1:29">
+      <c r="A9" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="25"/>
-      <c r="P9" s="25"/>
-      <c r="Q9" s="25"/>
-      <c r="S9" s="25"/>
-      <c r="T9" s="25"/>
-      <c r="U9" s="25"/>
-      <c r="V9" s="25"/>
-      <c r="W9" s="25"/>
-      <c r="X9" s="25"/>
-      <c r="Y9" s="25"/>
-    </row>
-    <row r="10" spans="1:28">
-      <c r="A10" s="23" t="s">
+      <c r="E9" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="Q9" s="22"/>
+      <c r="R9" s="22"/>
+      <c r="T9" s="22"/>
+      <c r="U9" s="22"/>
+      <c r="V9" s="22"/>
+      <c r="W9" s="22"/>
+      <c r="X9" s="22"/>
+      <c r="Y9" s="22"/>
+      <c r="Z9" s="22"/>
+    </row>
+    <row r="10" spans="1:29">
+      <c r="A10" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26">
+      <c r="E10" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23">
         <v>1</v>
       </c>
-      <c r="J10" s="26">
+      <c r="K10" s="23">
         <v>2</v>
       </c>
-      <c r="K10" s="26">
+      <c r="L10" s="23">
         <v>2</v>
       </c>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26">
+      <c r="M10" s="23"/>
+      <c r="N10" s="23">
         <v>2</v>
       </c>
-      <c r="N10" s="26"/>
-      <c r="P10" s="26">
+      <c r="O10" s="23"/>
+      <c r="Q10" s="23">
         <v>1</v>
       </c>
-      <c r="Q10" s="26"/>
-      <c r="S10" s="26"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="26">
+      <c r="R10" s="23"/>
+      <c r="T10" s="23"/>
+      <c r="U10" s="23"/>
+      <c r="V10" s="23">
         <v>2</v>
       </c>
-      <c r="V10" s="26"/>
-      <c r="W10" s="26"/>
-      <c r="X10" s="26"/>
-      <c r="Y10" s="26"/>
-    </row>
-    <row r="11" spans="1:28">
-      <c r="A11" s="21" t="s">
+      <c r="W10" s="23"/>
+      <c r="X10" s="23"/>
+      <c r="Y10" s="23"/>
+      <c r="Z10" s="23"/>
+    </row>
+    <row r="11" spans="1:29">
+      <c r="A11" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="J11" s="25">
+      <c r="E11" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="K11" s="22">
         <v>2</v>
       </c>
-      <c r="K11" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="L11" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="M11" s="25">
+      <c r="L11" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="M11" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="N11" s="22">
         <v>2</v>
       </c>
-      <c r="N11" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="P11" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q11" s="25">
+      <c r="O11" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q11" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="R11" s="22">
         <v>2</v>
       </c>
-      <c r="S11" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="T11" s="25">
+      <c r="T11" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="U11" s="22">
         <v>2</v>
       </c>
-      <c r="U11" s="25">
+      <c r="V11" s="22">
         <v>2</v>
       </c>
-      <c r="V11" s="25" t="s">
+      <c r="W11" s="22" t="s">
         <v>294</v>
       </c>
-      <c r="W11" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="X11" s="29">
+      <c r="X11" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="Y11" s="26">
         <v>2</v>
       </c>
-      <c r="Y11" s="25"/>
-    </row>
-    <row r="12" spans="1:28">
-      <c r="A12" s="23" t="s">
+      <c r="Z11" s="22"/>
+    </row>
+    <row r="12" spans="1:29">
+      <c r="A12" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="F12" s="26">
+      <c r="E12" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="G12" s="23">
         <v>1</v>
       </c>
-      <c r="G12" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="L12" s="26"/>
-      <c r="M12" s="26"/>
-      <c r="N12" s="26">
+      <c r="H12" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="I12" s="23"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23">
         <v>1</v>
       </c>
-      <c r="P12" s="26"/>
-      <c r="Q12" s="26"/>
-      <c r="S12" s="26"/>
-      <c r="T12" s="26"/>
-      <c r="U12" s="26"/>
-      <c r="V12" s="26"/>
-      <c r="W12" s="26"/>
-      <c r="X12" s="26"/>
-      <c r="Y12" s="26"/>
-    </row>
-    <row r="13" spans="1:28">
-      <c r="A13" s="21" t="s">
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
+      <c r="T12" s="23"/>
+      <c r="U12" s="23"/>
+      <c r="V12" s="23"/>
+      <c r="W12" s="23"/>
+      <c r="X12" s="23"/>
+      <c r="Y12" s="23"/>
+      <c r="Z12" s="23"/>
+    </row>
+    <row r="13" spans="1:29">
+      <c r="A13" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D13" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="F13" s="22">
         <v>1</v>
       </c>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25">
+      <c r="G13" s="22"/>
+      <c r="H13" s="22">
         <v>3</v>
       </c>
-      <c r="H13" s="25">
+      <c r="I13" s="22">
         <v>1</v>
       </c>
-      <c r="I13" s="25">
+      <c r="J13" s="22">
         <v>1</v>
       </c>
-      <c r="J13" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="K13" s="25">
+      <c r="K13" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="L13" s="22">
         <v>4</v>
       </c>
-      <c r="L13" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="M13" s="25"/>
-      <c r="N13" s="25">
+      <c r="M13" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22">
         <v>2</v>
       </c>
-      <c r="P13" s="25"/>
-      <c r="Q13" s="25"/>
-      <c r="S13" s="25">
+      <c r="Q13" s="22"/>
+      <c r="R13" s="22"/>
+      <c r="T13" s="22">
         <v>2</v>
       </c>
-      <c r="T13" s="25"/>
-      <c r="U13" s="25"/>
-      <c r="V13" s="25">
+      <c r="U13" s="22"/>
+      <c r="V13" s="22"/>
+      <c r="W13" s="22">
         <v>1</v>
       </c>
-      <c r="W13" s="25"/>
-      <c r="X13" s="25"/>
-      <c r="Y13" s="25">
+      <c r="X13" s="22"/>
+      <c r="Y13" s="22"/>
+      <c r="Z13" s="22">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:28">
-      <c r="A14" s="23" t="s">
+    <row r="14" spans="1:29">
+      <c r="A14" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="G14" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="H14" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="I14" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="L14" s="26"/>
-      <c r="M14" s="26"/>
-      <c r="N14" s="26"/>
-      <c r="P14" s="26"/>
-      <c r="Q14" s="26" t="s">
+      <c r="E14" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="H14" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="I14" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="J14" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23" t="s">
         <v>295</v>
       </c>
-      <c r="S14" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="T14" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="U14" s="26"/>
-      <c r="V14" s="26"/>
-      <c r="W14" s="26"/>
-      <c r="X14" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="Y14" s="26"/>
-    </row>
-    <row r="15" spans="1:28">
-      <c r="A15" s="21" t="s">
+      <c r="T14" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="U14" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="V14" s="23"/>
+      <c r="W14" s="23"/>
+      <c r="X14" s="23"/>
+      <c r="Y14" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z14" s="23"/>
+    </row>
+    <row r="15" spans="1:29">
+      <c r="A15" s="18" t="s">
         <v>94</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -8613,1018 +8789,1085 @@
       <c r="C15" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="E15" s="8"/>
+      <c r="E15" s="18" t="s">
+        <v>96</v>
+      </c>
       <c r="F15" s="8"/>
-      <c r="G15" s="8" t="s">
-        <v>292</v>
-      </c>
+      <c r="G15" s="8"/>
       <c r="H15" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="K15" s="8"/>
+      <c r="I15" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8" t="s">
+        <v>292</v>
+      </c>
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
-      <c r="P15" s="8"/>
+      <c r="O15" s="8"/>
       <c r="Q15" s="8"/>
-      <c r="S15" s="8"/>
+      <c r="R15" s="8"/>
       <c r="T15" s="8"/>
       <c r="U15" s="8"/>
       <c r="V15" s="8"/>
       <c r="W15" s="8"/>
       <c r="X15" s="8"/>
       <c r="Y15" s="8"/>
-    </row>
-    <row r="16" spans="1:28">
-      <c r="A16" s="23" t="s">
+      <c r="Z15" s="8"/>
+    </row>
+    <row r="16" spans="1:29">
+      <c r="A16" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="D16" s="23" t="s">
+      <c r="D16" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="E16" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="H16" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="25"/>
-      <c r="N16" s="25"/>
-      <c r="P16" s="25"/>
-      <c r="Q16" s="25"/>
-      <c r="S16" s="25"/>
-      <c r="T16" s="25"/>
-      <c r="U16" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="V16" s="25">
+      <c r="E16" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="I16" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="22"/>
+      <c r="T16" s="22"/>
+      <c r="U16" s="22"/>
+      <c r="V16" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="W16" s="22">
         <v>1</v>
       </c>
-      <c r="W16" s="25"/>
-      <c r="X16" s="25">
+      <c r="X16" s="22"/>
+      <c r="Y16" s="22">
         <v>2</v>
       </c>
-      <c r="Y16" s="25"/>
-    </row>
-    <row r="17" spans="1:25">
-      <c r="A17" s="21" t="s">
+      <c r="Z16" s="22"/>
+    </row>
+    <row r="17" spans="1:26">
+      <c r="A17" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="D17" s="21" t="s">
+      <c r="D17" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="G17" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="J17" s="26">
+      <c r="E17" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="H17" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="I17" s="23"/>
+      <c r="J17" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="K17" s="23">
         <v>2</v>
       </c>
-      <c r="K17" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="L17" s="26">
+      <c r="L17" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="M17" s="23">
         <v>2</v>
-      </c>
-      <c r="M17" s="11" t="s">
-        <v>296</v>
       </c>
       <c r="N17" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="P17" s="11" t="s">
+      <c r="O17" s="11" t="s">
         <v>296</v>
       </c>
       <c r="Q17" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="S17" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="T17" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="U17" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="V17" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="W17" s="26" t="s">
+      <c r="R17" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="T17" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="U17" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="V17" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="W17" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="X17" s="23" t="s">
         <v>293</v>
       </c>
-      <c r="X17" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="Y17" s="26" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25">
-      <c r="A18" s="23" t="s">
+      <c r="Y17" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z17" s="23" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26">
+      <c r="A18" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="D18" s="23" t="s">
+      <c r="D18" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="J18" s="25">
+      <c r="E18" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="K18" s="22">
         <v>2</v>
       </c>
-      <c r="K18" s="25"/>
-      <c r="L18" s="25"/>
-      <c r="M18" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="N18" s="25"/>
-      <c r="P18" s="25"/>
-      <c r="Q18" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="S18" s="25"/>
-      <c r="T18" s="25"/>
-      <c r="U18" s="25"/>
-      <c r="V18" s="25"/>
-      <c r="W18" s="25"/>
-      <c r="X18" s="25"/>
-      <c r="Y18" s="25"/>
-    </row>
-    <row r="19" spans="1:25">
-      <c r="A19" s="21" t="s">
+      <c r="L18" s="22"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="O18" s="22"/>
+      <c r="Q18" s="22"/>
+      <c r="R18" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="T18" s="22"/>
+      <c r="U18" s="22"/>
+      <c r="V18" s="22"/>
+      <c r="W18" s="22"/>
+      <c r="X18" s="22"/>
+      <c r="Y18" s="22"/>
+      <c r="Z18" s="22"/>
+    </row>
+    <row r="19" spans="1:26">
+      <c r="A19" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C19" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="D19" s="21" t="s">
+      <c r="D19" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="26">
+      <c r="E19" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="23">
         <v>3</v>
       </c>
-      <c r="L19" s="26"/>
-      <c r="M19" s="26"/>
-      <c r="N19" s="26"/>
-      <c r="P19" s="26"/>
-      <c r="Q19" s="26"/>
-      <c r="S19" s="26"/>
-      <c r="T19" s="26"/>
-      <c r="U19" s="26"/>
-      <c r="V19" s="26"/>
-      <c r="W19" s="26"/>
-      <c r="X19" s="26"/>
-      <c r="Y19" s="26"/>
-    </row>
-    <row r="20" spans="1:25">
-      <c r="A20" s="23" t="s">
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="23"/>
+      <c r="T19" s="23"/>
+      <c r="U19" s="23"/>
+      <c r="V19" s="23"/>
+      <c r="W19" s="23"/>
+      <c r="X19" s="23"/>
+      <c r="Y19" s="23"/>
+      <c r="Z19" s="23"/>
+    </row>
+    <row r="20" spans="1:26">
+      <c r="A20" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="C20" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="D20" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="E20" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="F20" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="G20" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="H20" s="25" t="s">
+      <c r="E20" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="G20" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="H20" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="I20" s="22" t="s">
         <v>295</v>
       </c>
-      <c r="I20" s="25"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="M20" s="25"/>
-      <c r="N20" s="25"/>
-      <c r="P20" s="25"/>
-      <c r="Q20" s="25"/>
-      <c r="S20" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="T20" s="29">
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="Q20" s="22"/>
+      <c r="R20" s="22"/>
+      <c r="T20" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="U20" s="26">
         <v>2</v>
       </c>
-      <c r="U20" s="25"/>
-      <c r="V20" s="25"/>
-      <c r="W20" s="25"/>
-      <c r="X20" s="25"/>
-      <c r="Y20" s="25"/>
-    </row>
-    <row r="21" spans="1:25">
-      <c r="A21" s="21" t="s">
+      <c r="V20" s="22"/>
+      <c r="W20" s="22"/>
+      <c r="X20" s="22"/>
+      <c r="Y20" s="22"/>
+      <c r="Z20" s="22"/>
+    </row>
+    <row r="21" spans="1:26">
+      <c r="A21" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="C21" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="D21" s="21" t="s">
+      <c r="D21" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="E21" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="K21" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="L21" s="26"/>
-      <c r="M21" s="26"/>
-      <c r="N21" s="26"/>
-      <c r="P21" s="26"/>
-      <c r="Q21" s="26"/>
-      <c r="S21" s="26"/>
-      <c r="T21" s="26"/>
-      <c r="U21" s="26"/>
-      <c r="V21" s="26"/>
-      <c r="W21" s="26"/>
-      <c r="X21" s="26"/>
-      <c r="Y21" s="26"/>
-    </row>
-    <row r="22" spans="1:25">
-      <c r="A22" s="23" t="s">
+      <c r="E21" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="F21" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="L21" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="M21" s="23"/>
+      <c r="N21" s="23"/>
+      <c r="O21" s="23"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="23"/>
+      <c r="T21" s="23"/>
+      <c r="U21" s="23"/>
+      <c r="V21" s="23"/>
+      <c r="W21" s="23"/>
+      <c r="X21" s="23"/>
+      <c r="Y21" s="23"/>
+      <c r="Z21" s="23"/>
+    </row>
+    <row r="22" spans="1:26">
+      <c r="A22" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="D22" s="23" t="s">
+      <c r="D22" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="E22" s="25">
+      <c r="E22" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="F22" s="22">
         <v>1</v>
       </c>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25"/>
-      <c r="J22" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="K22" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="L22" s="25">
+      <c r="G22" s="22"/>
+      <c r="H22" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="M22" s="22">
         <v>3</v>
       </c>
-      <c r="M22" s="25"/>
-      <c r="N22" s="25"/>
-      <c r="P22" s="25"/>
-      <c r="Q22" s="25"/>
-      <c r="S22" s="25"/>
-      <c r="T22" s="25"/>
-      <c r="U22" s="25"/>
-      <c r="V22" s="25"/>
-      <c r="W22" s="25"/>
-      <c r="X22" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="Y22" s="25"/>
-    </row>
-    <row r="23" spans="1:25">
-      <c r="A23" s="21" t="s">
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="Q22" s="22"/>
+      <c r="R22" s="22"/>
+      <c r="T22" s="22"/>
+      <c r="U22" s="22"/>
+      <c r="V22" s="22"/>
+      <c r="W22" s="22"/>
+      <c r="X22" s="22"/>
+      <c r="Y22" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z22" s="22"/>
+    </row>
+    <row r="23" spans="1:26">
+      <c r="A23" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="D23" s="21" t="s">
+      <c r="D23" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="E23" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="I23" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="J23" s="26">
+      <c r="E23" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="F23" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="G23" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="J23" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="K23" s="23">
         <v>2</v>
       </c>
-      <c r="K23" s="26"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="P23" s="26"/>
-      <c r="Q23" s="26" t="s">
+      <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="23"/>
+      <c r="O23" s="23"/>
+      <c r="Q23" s="23"/>
+      <c r="R23" s="23" t="s">
         <v>295</v>
       </c>
-      <c r="S23" s="26"/>
-      <c r="T23" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="U23" s="26"/>
-      <c r="V23" s="26"/>
-      <c r="W23" s="26"/>
-      <c r="X23" s="26"/>
-      <c r="Y23" s="26"/>
-    </row>
-    <row r="24" spans="1:25">
-      <c r="A24" s="23" t="s">
+      <c r="T23" s="23"/>
+      <c r="U23" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="V23" s="23"/>
+      <c r="W23" s="23"/>
+      <c r="X23" s="23"/>
+      <c r="Y23" s="23"/>
+      <c r="Z23" s="23"/>
+    </row>
+    <row r="24" spans="1:26">
+      <c r="A24" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="C24" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="D24" s="23" t="s">
+      <c r="D24" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="E24" s="25">
+      <c r="E24" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="F24" s="22">
         <v>1</v>
       </c>
-      <c r="F24" s="25">
+      <c r="G24" s="22">
         <v>1</v>
       </c>
-      <c r="G24" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="H24" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="I24" s="25"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="L24" s="25">
+      <c r="H24" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="I24" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="M24" s="22">
         <v>2</v>
       </c>
-      <c r="M24" s="25"/>
-      <c r="N24" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="P24" s="25"/>
-      <c r="Q24" s="25"/>
-      <c r="S24" s="25"/>
-      <c r="T24" s="25"/>
-      <c r="U24" s="25"/>
-      <c r="V24" s="25"/>
-      <c r="W24" s="25"/>
-      <c r="X24" s="25"/>
-      <c r="Y24" s="25"/>
-    </row>
-    <row r="25" spans="1:25">
-      <c r="A25" s="21" t="s">
+      <c r="N24" s="22"/>
+      <c r="O24" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q24" s="22"/>
+      <c r="R24" s="22"/>
+      <c r="T24" s="22"/>
+      <c r="U24" s="22"/>
+      <c r="V24" s="22"/>
+      <c r="W24" s="22"/>
+      <c r="X24" s="22"/>
+      <c r="Y24" s="22"/>
+      <c r="Z24" s="22"/>
+    </row>
+    <row r="25" spans="1:26">
+      <c r="A25" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="C25" s="21" t="s">
+      <c r="C25" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="D25" s="21" t="s">
+      <c r="D25" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
-      <c r="K25" s="26"/>
-      <c r="L25" s="26"/>
-      <c r="M25" s="26"/>
-      <c r="N25" s="26"/>
-      <c r="P25" s="26"/>
-      <c r="Q25" s="26"/>
-      <c r="S25" s="26"/>
-      <c r="T25" s="26"/>
-      <c r="U25" s="26"/>
-      <c r="V25" s="26"/>
-      <c r="W25" s="26"/>
-      <c r="X25" s="26"/>
-      <c r="Y25" s="26"/>
-    </row>
-    <row r="26" spans="1:25">
-      <c r="A26" s="23" t="s">
+      <c r="E25" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="23"/>
+      <c r="N25" s="23"/>
+      <c r="O25" s="23"/>
+      <c r="Q25" s="23"/>
+      <c r="R25" s="23"/>
+      <c r="T25" s="23"/>
+      <c r="U25" s="23"/>
+      <c r="V25" s="23"/>
+      <c r="W25" s="23"/>
+      <c r="X25" s="23"/>
+      <c r="Y25" s="23"/>
+      <c r="Z25" s="23"/>
+    </row>
+    <row r="26" spans="1:26">
+      <c r="A26" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="B26" s="20" t="s">
+      <c r="B26" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="C26" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="D26" s="23" t="s">
+      <c r="D26" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="E26" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="F26" s="25">
+      <c r="E26" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="F26" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="G26" s="22">
         <v>1</v>
       </c>
-      <c r="G26" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="H26" s="28" t="s">
-        <v>295</v>
+      <c r="H26" s="22" t="s">
+        <v>292</v>
       </c>
       <c r="I26" s="25" t="s">
         <v>295</v>
       </c>
-      <c r="J26" s="25">
+      <c r="J26" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="K26" s="22">
         <v>2</v>
       </c>
-      <c r="K26" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="L26" s="25">
+      <c r="L26" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="M26" s="22">
         <v>2</v>
       </c>
-      <c r="M26" s="25" t="s">
+      <c r="N26" s="22" t="s">
         <v>295</v>
       </c>
-      <c r="N26" s="25">
+      <c r="O26" s="22">
         <v>1</v>
       </c>
-      <c r="P26" s="25"/>
-      <c r="Q26" s="25"/>
-      <c r="S26" s="25">
+      <c r="Q26" s="22"/>
+      <c r="R26" s="22"/>
+      <c r="T26" s="22">
         <v>1</v>
       </c>
-      <c r="T26" s="29">
+      <c r="U26" s="26">
         <v>2</v>
       </c>
-      <c r="U26" s="25" t="s">
+      <c r="V26" s="22" t="s">
         <v>295</v>
       </c>
-      <c r="V26" s="25"/>
-      <c r="W26" s="30">
+      <c r="W26" s="22"/>
+      <c r="X26" s="27">
         <v>1</v>
       </c>
-      <c r="X26" s="25"/>
-      <c r="Y26" s="25" t="s">
+      <c r="Y26" s="22"/>
+      <c r="Z26" s="22" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
-      <c r="A27" s="21" t="s">
+    <row r="27" spans="1:26">
+      <c r="A27" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="21" t="s">
+      <c r="C27" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="D27" s="21" t="s">
+      <c r="D27" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="J27" s="26"/>
-      <c r="K27" s="26"/>
-      <c r="L27" s="26"/>
-      <c r="M27" s="26"/>
-      <c r="N27" s="26"/>
-      <c r="P27" s="26"/>
-      <c r="Q27" s="26"/>
-      <c r="S27" s="26"/>
-      <c r="T27" s="26"/>
-      <c r="U27" s="26"/>
-      <c r="V27" s="26"/>
-      <c r="W27" s="26"/>
-      <c r="X27" s="26"/>
-      <c r="Y27" s="26"/>
-    </row>
-    <row r="28" spans="1:25">
-      <c r="A28" s="23" t="s">
+      <c r="E27" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="H27" s="23"/>
+      <c r="I27" s="23"/>
+      <c r="J27" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="K27" s="23"/>
+      <c r="L27" s="23"/>
+      <c r="M27" s="23"/>
+      <c r="N27" s="23"/>
+      <c r="O27" s="23"/>
+      <c r="Q27" s="23"/>
+      <c r="R27" s="23"/>
+      <c r="T27" s="23"/>
+      <c r="U27" s="23"/>
+      <c r="V27" s="23"/>
+      <c r="W27" s="23"/>
+      <c r="X27" s="23"/>
+      <c r="Y27" s="23"/>
+      <c r="Z27" s="23"/>
+    </row>
+    <row r="28" spans="1:26">
+      <c r="A28" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="B28" s="20" t="s">
+      <c r="B28" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="D28" s="23" t="s">
+      <c r="D28" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="E28" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25">
+      <c r="E28" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="F28" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22">
         <v>4</v>
       </c>
-      <c r="H28" s="25">
+      <c r="I28" s="22">
         <v>1</v>
       </c>
-      <c r="I28" s="25"/>
-      <c r="J28" s="25"/>
-      <c r="K28" s="25"/>
-      <c r="L28" s="25">
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="22">
         <v>1</v>
       </c>
-      <c r="M28" s="25" t="s">
+      <c r="N28" s="22" t="s">
         <v>295</v>
       </c>
-      <c r="N28" s="29">
+      <c r="O28" s="26">
         <v>2</v>
       </c>
-      <c r="P28" s="25"/>
-      <c r="Q28" s="29">
+      <c r="Q28" s="22"/>
+      <c r="R28" s="26">
         <v>2</v>
       </c>
-      <c r="S28" s="25"/>
-      <c r="T28" s="25"/>
-      <c r="U28" s="25"/>
-      <c r="V28" s="25"/>
-      <c r="W28" s="29">
+      <c r="T28" s="22"/>
+      <c r="U28" s="22"/>
+      <c r="V28" s="22"/>
+      <c r="W28" s="22"/>
+      <c r="X28" s="26">
         <v>5</v>
       </c>
-      <c r="X28" s="25"/>
-      <c r="Y28" s="25" t="s">
+      <c r="Y28" s="22"/>
+      <c r="Z28" s="22" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
-      <c r="A29" s="21" t="s">
+    <row r="29" spans="1:26">
+      <c r="A29" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="C29" s="21" t="s">
+      <c r="C29" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="D29" s="21" t="s">
+      <c r="D29" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="E29" s="26" t="s">
+      <c r="E29" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="F29" s="23" t="s">
         <v>293</v>
       </c>
-      <c r="F29" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="G29" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="K29" s="26"/>
-      <c r="L29" s="26"/>
-      <c r="M29" s="26"/>
-      <c r="N29" s="26"/>
-      <c r="P29" s="26"/>
-      <c r="Q29" s="26"/>
-      <c r="S29" s="26"/>
-      <c r="T29" s="26"/>
-      <c r="U29" s="26"/>
-      <c r="V29" s="26"/>
-      <c r="W29" s="26"/>
-      <c r="X29" s="26"/>
-      <c r="Y29" s="26"/>
-    </row>
-    <row r="30" spans="1:25">
-      <c r="A30" s="23" t="s">
+      <c r="G29" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="H29" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="I29" s="23"/>
+      <c r="J29" s="23"/>
+      <c r="K29" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="L29" s="23"/>
+      <c r="M29" s="23"/>
+      <c r="N29" s="23"/>
+      <c r="O29" s="23"/>
+      <c r="Q29" s="23"/>
+      <c r="R29" s="23"/>
+      <c r="T29" s="23"/>
+      <c r="U29" s="23"/>
+      <c r="V29" s="23"/>
+      <c r="W29" s="23"/>
+      <c r="X29" s="23"/>
+      <c r="Y29" s="23"/>
+      <c r="Z29" s="23"/>
+    </row>
+    <row r="30" spans="1:26">
+      <c r="A30" s="20" t="s">
         <v>218</v>
       </c>
-      <c r="B30" s="20" t="s">
+      <c r="B30" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="C30" s="20" t="s">
+      <c r="C30" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="D30" s="23" t="s">
+      <c r="D30" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25" t="s">
+      <c r="E30" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="H30" s="25"/>
-      <c r="I30" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="J30" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="K30" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="L30" s="25"/>
-      <c r="M30" s="25"/>
-      <c r="N30" s="25"/>
-      <c r="P30" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q30" s="25"/>
-      <c r="S30" s="25"/>
-      <c r="T30" s="25"/>
-      <c r="U30" s="25"/>
-      <c r="V30" s="25"/>
-      <c r="W30" s="25"/>
-      <c r="X30" s="25"/>
-      <c r="Y30" s="25"/>
-    </row>
-    <row r="31" spans="1:25">
-      <c r="A31" s="21" t="s">
+      <c r="I30" s="22"/>
+      <c r="J30" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="K30" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="L30" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="22"/>
+      <c r="Q30" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="R30" s="22"/>
+      <c r="T30" s="22"/>
+      <c r="U30" s="22"/>
+      <c r="V30" s="22"/>
+      <c r="W30" s="22"/>
+      <c r="X30" s="22"/>
+      <c r="Y30" s="22"/>
+      <c r="Z30" s="22"/>
+    </row>
+    <row r="31" spans="1:26">
+      <c r="A31" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="B31" s="21" t="s">
+      <c r="B31" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="C31" s="21" t="s">
+      <c r="C31" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="D31" s="21" t="s">
+      <c r="D31" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="K31" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="L31" s="26">
+      <c r="E31" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="L31" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="M31" s="23">
         <v>1</v>
       </c>
-      <c r="M31" s="26">
+      <c r="N31" s="23">
         <v>2</v>
       </c>
-      <c r="N31" s="26"/>
-      <c r="P31" s="26">
+      <c r="O31" s="23"/>
+      <c r="Q31" s="23">
         <v>1</v>
       </c>
-      <c r="Q31" s="26"/>
-      <c r="S31" s="26"/>
-      <c r="T31" s="26">
+      <c r="R31" s="23"/>
+      <c r="T31" s="23"/>
+      <c r="U31" s="23">
         <v>2</v>
       </c>
-      <c r="U31" s="26"/>
-      <c r="V31" s="26">
+      <c r="V31" s="23"/>
+      <c r="W31" s="23">
         <v>1</v>
       </c>
-      <c r="W31" s="26"/>
-      <c r="X31" s="26">
+      <c r="X31" s="23"/>
+      <c r="Y31" s="23">
         <v>2</v>
       </c>
-      <c r="Y31" s="31">
+      <c r="Z31" s="28">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:25">
-      <c r="A32" s="23" t="s">
+    <row r="32" spans="1:26">
+      <c r="A32" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B32" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C32" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="D32" s="23" t="s">
+      <c r="D32" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="G32" s="25">
+      <c r="E32" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="H32" s="22">
         <v>2</v>
       </c>
-      <c r="H32" s="25"/>
-      <c r="I32" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="J32" s="25"/>
-      <c r="K32" s="25"/>
-      <c r="L32" s="25"/>
-      <c r="M32" s="25"/>
-      <c r="N32" s="25"/>
-      <c r="P32" s="25"/>
-      <c r="Q32" s="25" t="s">
+      <c r="I32" s="22"/>
+      <c r="J32" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="Q32" s="22"/>
+      <c r="R32" s="22" t="s">
         <v>295</v>
       </c>
-      <c r="S32" s="25"/>
-      <c r="T32" s="25"/>
-      <c r="U32" s="25"/>
-      <c r="V32" s="25"/>
-      <c r="W32" s="25"/>
-      <c r="X32" s="25"/>
-      <c r="Y32" s="25"/>
-    </row>
-    <row r="33" spans="1:25">
-      <c r="A33" s="21" t="s">
+      <c r="T32" s="22"/>
+      <c r="U32" s="22"/>
+      <c r="V32" s="22"/>
+      <c r="W32" s="22"/>
+      <c r="X32" s="22"/>
+      <c r="Y32" s="22"/>
+      <c r="Z32" s="22"/>
+    </row>
+    <row r="33" spans="1:26">
+      <c r="A33" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="B33" s="21" t="s">
+      <c r="B33" s="18" t="s">
         <v>251</v>
       </c>
-      <c r="C33" s="21" t="s">
+      <c r="C33" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="D33" s="21" t="s">
+      <c r="D33" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="E33" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="F33" s="26" t="s">
+      <c r="E33" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="F33" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="G33" s="23" t="s">
         <v>293</v>
       </c>
-      <c r="G33" s="26">
+      <c r="H33" s="23">
         <v>3</v>
       </c>
-      <c r="H33" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="I33" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="J33" s="26">
+      <c r="I33" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="J33" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="K33" s="23">
         <v>2</v>
       </c>
-      <c r="K33" s="26">
+      <c r="L33" s="23">
         <v>2</v>
       </c>
-      <c r="L33" s="26">
+      <c r="M33" s="23">
         <v>3</v>
       </c>
-      <c r="M33" s="26"/>
-      <c r="N33" s="26">
+      <c r="N33" s="23"/>
+      <c r="O33" s="23">
         <v>3</v>
       </c>
-      <c r="P33" s="26"/>
-      <c r="Q33" s="26"/>
-      <c r="S33" s="26"/>
-      <c r="T33" s="26">
+      <c r="Q33" s="23"/>
+      <c r="R33" s="23"/>
+      <c r="T33" s="23"/>
+      <c r="U33" s="23">
         <v>3</v>
       </c>
-      <c r="U33" s="26"/>
-      <c r="V33" s="26">
+      <c r="V33" s="23"/>
+      <c r="W33" s="23">
         <v>1</v>
       </c>
-      <c r="W33" s="31">
+      <c r="X33" s="28">
         <v>5</v>
       </c>
-      <c r="X33" s="26"/>
-      <c r="Y33" s="26">
+      <c r="Y33" s="23"/>
+      <c r="Z33" s="23">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
-      <c r="A34" s="23" t="s">
+    <row r="34" spans="1:26">
+      <c r="A34" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="B34" s="20" t="s">
+      <c r="B34" s="17" t="s">
         <v>261</v>
       </c>
-      <c r="C34" s="20" t="s">
+      <c r="C34" s="17" t="s">
         <v>260</v>
       </c>
-      <c r="D34" s="23" t="s">
+      <c r="D34" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="E34" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="F34" s="25">
+      <c r="E34" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="F34" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="G34" s="22">
         <v>1</v>
       </c>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="I34" s="28" t="s">
+      <c r="H34" s="22"/>
+      <c r="I34" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="J34" s="25" t="s">
         <v>295</v>
       </c>
-      <c r="J34" s="25"/>
-      <c r="K34" s="25"/>
-      <c r="L34" s="25"/>
-      <c r="M34" s="25"/>
-      <c r="N34" s="25"/>
-      <c r="P34" s="25"/>
-      <c r="Q34" s="25"/>
-      <c r="S34" s="25"/>
-      <c r="T34" s="25"/>
-      <c r="U34" s="25"/>
-      <c r="V34" s="25"/>
-      <c r="W34" s="25"/>
-      <c r="X34" s="25"/>
-      <c r="Y34" s="25"/>
-    </row>
-    <row r="35" spans="1:25">
-      <c r="A35" s="21" t="s">
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="22"/>
+      <c r="N34" s="22"/>
+      <c r="O34" s="22"/>
+      <c r="Q34" s="22"/>
+      <c r="R34" s="22"/>
+      <c r="T34" s="22"/>
+      <c r="U34" s="22"/>
+      <c r="V34" s="22"/>
+      <c r="W34" s="22"/>
+      <c r="X34" s="22"/>
+      <c r="Y34" s="22"/>
+      <c r="Z34" s="22"/>
+    </row>
+    <row r="35" spans="1:26">
+      <c r="A35" s="18" t="s">
         <v>267</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="B35" s="18" t="s">
         <v>272</v>
       </c>
-      <c r="C35" s="21" t="s">
+      <c r="C35" s="18" t="s">
         <v>270</v>
       </c>
-      <c r="D35" s="21" t="s">
+      <c r="D35" s="18" t="s">
         <v>268</v>
       </c>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="K35" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="L35" s="26">
+      <c r="E35" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="23"/>
+      <c r="I35" s="23"/>
+      <c r="J35" s="23"/>
+      <c r="K35" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="L35" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="M35" s="23">
         <v>2</v>
       </c>
-      <c r="M35" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="N35" s="26"/>
-      <c r="P35" s="26"/>
-      <c r="Q35" s="26"/>
-      <c r="S35" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="T35" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="U35" s="26"/>
-      <c r="V35" s="26"/>
-      <c r="W35" s="26"/>
-      <c r="X35" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="Y35" s="26" t="s">
+      <c r="N35" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="O35" s="23"/>
+      <c r="Q35" s="23"/>
+      <c r="R35" s="23"/>
+      <c r="T35" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="U35" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="V35" s="23"/>
+      <c r="W35" s="23"/>
+      <c r="X35" s="23"/>
+      <c r="Y35" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z35" s="23" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="36" spans="1:25">
-      <c r="A36" s="23" t="s">
+    <row r="36" spans="1:26">
+      <c r="A36" s="20" t="s">
         <v>279</v>
       </c>
-      <c r="B36" s="22" t="s">
+      <c r="B36" s="19" t="s">
         <v>283</v>
       </c>
-      <c r="C36" s="22" t="s">
+      <c r="C36" s="19" t="s">
         <v>282</v>
       </c>
-      <c r="D36" s="23" t="s">
+      <c r="D36" s="20" t="s">
         <v>280</v>
       </c>
-      <c r="E36" s="27" t="s">
-        <v>292</v>
-      </c>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27" t="s">
-        <v>292</v>
-      </c>
-      <c r="H36" s="27"/>
-      <c r="I36" s="27"/>
-      <c r="J36" s="27" t="s">
-        <v>292</v>
-      </c>
-      <c r="K36" s="27" t="s">
-        <v>292</v>
-      </c>
-      <c r="L36" s="27" t="s">
-        <v>292</v>
-      </c>
-      <c r="M36" s="27"/>
-      <c r="N36" s="27"/>
-      <c r="P36" s="27"/>
-      <c r="Q36" s="27"/>
-      <c r="S36" s="27"/>
-      <c r="T36" s="27"/>
-      <c r="U36" s="27"/>
-      <c r="V36" s="27"/>
-      <c r="W36" s="27"/>
-      <c r="X36" s="27"/>
-      <c r="Y36" s="27"/>
+      <c r="E36" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="F36" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="G36" s="24"/>
+      <c r="H36" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="I36" s="24"/>
+      <c r="J36" s="24"/>
+      <c r="K36" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="L36" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="M36" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="N36" s="24"/>
+      <c r="O36" s="24"/>
+      <c r="Q36" s="24"/>
+      <c r="R36" s="24"/>
+      <c r="T36" s="24"/>
+      <c r="U36" s="24"/>
+      <c r="V36" s="24"/>
+      <c r="W36" s="24"/>
+      <c r="X36" s="24"/>
+      <c r="Y36" s="24"/>
+      <c r="Z36" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="AA5:AB5"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:P5"/>
+  <mergeCells count="17">
+    <mergeCell ref="AB5:AC5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:Q5"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/Datos Tesis Upstream/Estructura de Datos/2526-3/Asistencia y Participaciones Estructura de Datos 2526-3.xlsx
+++ b/Datos Tesis Upstream/Estructura de Datos/2526-3/Asistencia y Participaciones Estructura de Datos 2526-3.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Lista" sheetId="1" r:id="rId1"/>
     <sheet name="Asistencia" sheetId="2" r:id="rId2"/>
     <sheet name="Estandar" sheetId="3" r:id="rId3"/>
+    <sheet name="Cronograma" sheetId="4" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -9872,4 +9873,340 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">semana</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dia_sesion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tema</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_sesion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>6</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>6</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>7</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>7</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>8</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>8</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>9</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>9</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>10</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>10</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>12</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>12</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>administrativa</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nota:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tema = código del catálogo de la asignatura. Si la sesión no cubre contenido nuevo: tema = 0 y tipo_sesion indica la causa (evaluacion, repaso, sin_clase, administrativa). Si tema &gt; 0 la sesión es de contenido y tipo_sesion queda vacío.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>